--- a/docs/downloads/04/tbl_origine_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_origine_alaotra_tous.xlsx
@@ -627,12 +627,6 @@
           <t>Valivotaka</t>
         </is>
       </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>4.4</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -765,12 +759,6 @@
           <t>Mpihavy</t>
         </is>
       </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <v>3.4</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -811,12 +799,6 @@
           <t>Valivotaka</t>
         </is>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -903,12 +885,6 @@
           <t>Valivotaka</t>
         </is>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>2.6</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -926,12 +902,6 @@
           <t>Zana-tany</t>
         </is>
       </c>
-      <c r="D25">
-        <v>4</v>
-      </c>
-      <c r="E25">
-        <v>10.5</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -995,12 +965,6 @@
           <t>Valivotaka</t>
         </is>
       </c>
-      <c r="D28">
-        <v>3</v>
-      </c>
-      <c r="E28">
-        <v>5.8</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1087,12 +1051,6 @@
           <t>Valivotaka</t>
         </is>
       </c>
-      <c r="D32">
-        <v>4</v>
-      </c>
-      <c r="E32">
-        <v>11.1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1110,12 +1068,6 @@
           <t>Zana-tany</t>
         </is>
       </c>
-      <c r="D33">
-        <v>4</v>
-      </c>
-      <c r="E33">
-        <v>11.1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1133,12 +1085,6 @@
           <t>Mpihavy</t>
         </is>
       </c>
-      <c r="D34">
-        <v>4</v>
-      </c>
-      <c r="E34">
-        <v>8.699999999999999</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1271,12 +1217,6 @@
           <t>Valivotaka</t>
         </is>
       </c>
-      <c r="D40">
-        <v>3</v>
-      </c>
-      <c r="E40">
-        <v>9.1</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1432,12 +1372,6 @@
           <t>Valivotaka</t>
         </is>
       </c>
-      <c r="D47">
-        <v>4</v>
-      </c>
-      <c r="E47">
-        <v>6.3</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1478,12 +1412,6 @@
           <t>Mpihavy</t>
         </is>
       </c>
-      <c r="D49">
-        <v>4</v>
-      </c>
-      <c r="E49">
-        <v>4.5</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1524,12 +1452,6 @@
           <t>Valivotaka</t>
         </is>
       </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1639,12 +1561,6 @@
           <t>Mpihavy</t>
         </is>
       </c>
-      <c r="D56">
-        <v>4</v>
-      </c>
-      <c r="E56">
-        <v>5.5</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1776,12 +1692,6 @@
         <is>
           <t>Valivotaka</t>
         </is>
-      </c>
-      <c r="D62">
-        <v>4</v>
-      </c>
-      <c r="E62">
-        <v>7.8</v>
       </c>
     </row>
     <row r="63">

--- a/docs/downloads/04/tbl_origine_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_origine_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -476,7 +476,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -522,7 +522,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -545,7 +545,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -568,7 +568,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -654,7 +654,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -786,7 +786,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -906,7 +906,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -952,7 +952,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -992,7 +992,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1038,7 +1038,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1089,7 +1089,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1112,7 +1112,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1158,7 +1158,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1181,7 +1181,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1204,7 +1204,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1336,7 +1336,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1359,7 +1359,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1376,7 +1376,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1416,7 +1416,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1456,7 +1456,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1502,7 +1502,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1548,7 +1548,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1565,7 +1565,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1588,7 +1588,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1634,7 +1634,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1680,7 +1680,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1697,7 +1697,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1720,7 +1720,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1743,7 +1743,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1766,7 +1766,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1812,7 +1812,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1858,7 +1858,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1881,7 +1881,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
